--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1578,6 +1578,3696 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127288413</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>753205</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7211601</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127288416</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>753107</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7211679</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127288414</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>753275</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7211522</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127288418</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>753102</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7211838</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127288456</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80152</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>753189</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7211853</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127288440</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>753266</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7211612</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127288412</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58516</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>753218</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7211643</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127288436</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>753266</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7211612</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127288458</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75130</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>753233</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7211574</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127288449</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>753175</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7211717</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127288430</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>753188</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7211856</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127288424</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98464</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>753214</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7211833</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127288457</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80152</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>753330</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7211606</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127288444</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>753279</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7211533</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127288447</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>753191</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7211761</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127288432</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>753324</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7211590</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127288438</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>753284</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7211602</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127288448</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>753191</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7211707</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127288434</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>753345</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7211616</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127288422</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57817</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>753107</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7211679</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lock</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127288425</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98464</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>753269</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7211606</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127288442</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>753219</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7211658</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127288453</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>753179</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7211888</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127288439</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>753269</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7211606</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127288441</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>753235</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7211650</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127288451</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>753241</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7211651</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127288431</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>753300</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7211568</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127288423</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80146</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>753266</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7211612</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127288428</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>753286</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7211540</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127288443</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>753011</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7211692</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127288445</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>753220</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7211637</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127288415</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>753247</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7211655</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127288433</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>753330</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7211606</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127288450</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>753255</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7211635</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127288419</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>753103</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7211845</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127288417</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57657</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>753086</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7211788</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127288455</v>
+      </c>
+      <c r="B46" t="n">
+        <v>80152</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>753192</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7211856</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2201,32 +2201,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288412</v>
+        <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>58516</v>
+        <v>80117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753218</v>
+        <v>753266</v>
       </c>
       <c r="R16" t="n">
-        <v>7211643</v>
+        <v>7211612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B17" t="n">
-        <v>80117</v>
+        <v>75130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R17" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288458</v>
+        <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>75130</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753233</v>
+        <v>753175</v>
       </c>
       <c r="R18" t="n">
-        <v>7211574</v>
+        <v>7211717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>80117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R19" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>80117</v>
+        <v>58516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R20" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,10 +1677,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127288416</v>
+        <v>127288414</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753107</v>
+        <v>753275</v>
       </c>
       <c r="R11" t="n">
-        <v>7211679</v>
+        <v>7211522</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,10 +1787,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127288414</v>
+        <v>127288416</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753275</v>
+        <v>753107</v>
       </c>
       <c r="R12" t="n">
-        <v>7211522</v>
+        <v>7211679</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,53 +1897,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>80156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R13" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B14" t="n">
-        <v>80152</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R14" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,6 +2073,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288458</v>
+        <v>127288449</v>
       </c>
       <c r="B17" t="n">
-        <v>75130</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753233</v>
+        <v>753175</v>
       </c>
       <c r="R17" t="n">
-        <v>7211574</v>
+        <v>7211717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R18" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>58520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R19" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288412</v>
+        <v>127288458</v>
       </c>
       <c r="B20" t="n">
-        <v>58516</v>
+        <v>75134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208249</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753218</v>
+        <v>753233</v>
       </c>
       <c r="R20" t="n">
-        <v>7211643</v>
+        <v>7211574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>127288457</v>
       </c>
       <c r="B22" t="n">
-        <v>80152</v>
+        <v>80156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127288444</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>127288447</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>127288432</v>
       </c>
       <c r="B25" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,32 +3176,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288438</v>
+        <v>127288448</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753284</v>
+        <v>753191</v>
       </c>
       <c r="R26" t="n">
-        <v>7211602</v>
+        <v>7211707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,6 +3247,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3273,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288448</v>
+        <v>127288434</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3308,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753191</v>
+        <v>753345</v>
       </c>
       <c r="R27" t="n">
-        <v>7211707</v>
+        <v>7211616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3344,11 +3349,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288434</v>
+        <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>80117</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753345</v>
+        <v>753284</v>
       </c>
       <c r="R28" t="n">
-        <v>7211616</v>
+        <v>7211602</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3475,7 +3475,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R31" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>98447</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R32" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288441</v>
+        <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>98443</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753235</v>
+        <v>753241</v>
       </c>
       <c r="R34" t="n">
-        <v>7211650</v>
+        <v>7211651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288451</v>
+        <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753241</v>
+        <v>753300</v>
       </c>
       <c r="R35" t="n">
-        <v>7211651</v>
+        <v>7211568</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288431</v>
+        <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>80117</v>
+        <v>98447</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753300</v>
+        <v>753235</v>
       </c>
       <c r="R36" t="n">
-        <v>7211568</v>
+        <v>7211650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288443</v>
+        <v>127288445</v>
       </c>
       <c r="B39" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,21 +4466,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753011</v>
+        <v>753220</v>
       </c>
       <c r="R39" t="n">
-        <v>7211692</v>
+        <v>7211637</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288445</v>
+        <v>127288443</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>91348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,21 +4563,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4587,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753220</v>
+        <v>753011</v>
       </c>
       <c r="R40" t="n">
-        <v>7211637</v>
+        <v>7211692</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4652,7 +4652,7 @@
         <v>127288415</v>
       </c>
       <c r="B41" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>127288433</v>
       </c>
       <c r="B42" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>127288450</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5063,53 +5063,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>57657</v>
+        <v>80156</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R45" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,11 +5134,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,45 +5160,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>80152</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R46" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,6 +5239,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B16" t="n">
-        <v>80121</v>
+        <v>75134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R16" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288449</v>
+        <v>127288436</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753175</v>
+        <v>753266</v>
       </c>
       <c r="R17" t="n">
-        <v>7211717</v>
+        <v>7211612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288430</v>
+        <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753188</v>
+        <v>753175</v>
       </c>
       <c r="R18" t="n">
-        <v>7211856</v>
+        <v>7211717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288412</v>
+        <v>127288430</v>
       </c>
       <c r="B19" t="n">
-        <v>58520</v>
+        <v>80121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753218</v>
+        <v>753188</v>
       </c>
       <c r="R19" t="n">
-        <v>7211643</v>
+        <v>7211856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288458</v>
+        <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>75134</v>
+        <v>58520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753233</v>
+        <v>753218</v>
       </c>
       <c r="R20" t="n">
-        <v>7211574</v>
+        <v>7211643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>80156</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R22" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>80156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R23" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3472,53 +3472,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288422</v>
+        <v>127288425</v>
       </c>
       <c r="B29" t="n">
-        <v>57821</v>
+        <v>98468</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753107</v>
+        <v>753269</v>
       </c>
       <c r="R29" t="n">
-        <v>7211679</v>
+        <v>7211606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,11 +3543,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,45 +3569,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288425</v>
+        <v>127288422</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>57821</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753269</v>
+        <v>753107</v>
       </c>
       <c r="R30" t="n">
-        <v>7211606</v>
+        <v>7211679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,6 +3648,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98447</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R31" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B32" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R32" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4466,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R39" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4534,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4649,10 +4662,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,42 +4673,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R41" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,11 +4733,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1897,45 +1897,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R13" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,6 +1976,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R14" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,11 +2078,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3472,45 +3472,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288425</v>
+        <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>98468</v>
+        <v>57821</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753269</v>
+        <v>753107</v>
       </c>
       <c r="R29" t="n">
-        <v>7211606</v>
+        <v>7211679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,6 +3551,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,53 +3582,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288422</v>
+        <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>57821</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753107</v>
+        <v>753269</v>
       </c>
       <c r="R30" t="n">
-        <v>7211679</v>
+        <v>7211606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,11 +3653,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,42 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R39" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4534,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4662,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4673,34 +4660,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R41" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4733,6 +4728,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4466,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R39" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4534,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4649,10 +4662,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,42 +4673,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R41" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,11 +4733,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1677,7 +1677,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127288414</v>
+        <v>127288416</v>
       </c>
       <c r="B11" t="n">
         <v>57661</v>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753275</v>
+        <v>753107</v>
       </c>
       <c r="R11" t="n">
-        <v>7211522</v>
+        <v>7211679</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1787,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127288416</v>
+        <v>127288414</v>
       </c>
       <c r="B12" t="n">
         <v>57661</v>
@@ -1830,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753107</v>
+        <v>753275</v>
       </c>
       <c r="R12" t="n">
-        <v>7211679</v>
+        <v>7211522</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,53 +1897,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R13" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B14" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R14" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,6 +2073,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288458</v>
+        <v>127288449</v>
       </c>
       <c r="B16" t="n">
-        <v>75134</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753233</v>
+        <v>753175</v>
       </c>
       <c r="R16" t="n">
-        <v>7211574</v>
+        <v>7211717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R18" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>58520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R19" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288412</v>
+        <v>127288458</v>
       </c>
       <c r="B20" t="n">
-        <v>58520</v>
+        <v>75134</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208249</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753218</v>
+        <v>753233</v>
       </c>
       <c r="R20" t="n">
-        <v>7211643</v>
+        <v>7211574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288432</v>
+        <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R25" t="n">
-        <v>7211590</v>
+        <v>7211707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3150,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,10 +3181,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288448</v>
+        <v>127288432</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3192,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753191</v>
+        <v>753324</v>
       </c>
       <c r="R26" t="n">
-        <v>7211707</v>
+        <v>7211590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,11 +3252,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>98447</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R31" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R32" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288451</v>
+        <v>127288441</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753241</v>
+        <v>753235</v>
       </c>
       <c r="R34" t="n">
-        <v>7211651</v>
+        <v>7211650</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288431</v>
+        <v>127288451</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753300</v>
+        <v>753241</v>
       </c>
       <c r="R35" t="n">
-        <v>7211568</v>
+        <v>7211651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288441</v>
+        <v>127288431</v>
       </c>
       <c r="B36" t="n">
-        <v>98447</v>
+        <v>80121</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753235</v>
+        <v>753300</v>
       </c>
       <c r="R36" t="n">
-        <v>7211650</v>
+        <v>7211568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288415</v>
+        <v>127288443</v>
       </c>
       <c r="B39" t="n">
-        <v>57661</v>
+        <v>91348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,42 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753247</v>
+        <v>753011</v>
       </c>
       <c r="R39" t="n">
-        <v>7211655</v>
+        <v>7211692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4534,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4565,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288443</v>
+        <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4576,21 +4563,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4600,10 +4587,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753011</v>
+        <v>753220</v>
       </c>
       <c r="R40" t="n">
-        <v>7211692</v>
+        <v>7211637</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4662,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>57661</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4673,34 +4660,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R41" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4733,6 +4728,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127288433</v>
+        <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>80121</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,21 +4770,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753330</v>
+        <v>753255</v>
       </c>
       <c r="R42" t="n">
-        <v>7211606</v>
+        <v>7211635</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127288450</v>
+        <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753255</v>
+        <v>753330</v>
       </c>
       <c r="R43" t="n">
-        <v>7211635</v>
+        <v>7211606</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5063,45 +5063,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B45" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R45" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5134,6 +5142,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5160,53 +5173,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R46" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,11 +5244,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R31" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B32" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R32" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288441</v>
+        <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753235</v>
+        <v>753241</v>
       </c>
       <c r="R34" t="n">
-        <v>7211650</v>
+        <v>7211651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288451</v>
+        <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>80121</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753241</v>
+        <v>753300</v>
       </c>
       <c r="R35" t="n">
-        <v>7211651</v>
+        <v>7211568</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288431</v>
+        <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>80121</v>
+        <v>98448</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753300</v>
+        <v>753235</v>
       </c>
       <c r="R36" t="n">
-        <v>7211568</v>
+        <v>7211650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5063,53 +5063,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>57661</v>
+        <v>80156</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R45" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,11 +5134,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,45 +5160,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>80156</v>
+        <v>57661</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R46" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,6 +5239,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127288456</v>
       </c>
       <c r="B13" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127288418</v>
       </c>
       <c r="B14" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288449</v>
+        <v>127288458</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>75136</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753175</v>
+        <v>753233</v>
       </c>
       <c r="R16" t="n">
-        <v>7211717</v>
+        <v>7211574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288436</v>
+        <v>127288449</v>
       </c>
       <c r="B17" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753266</v>
+        <v>753175</v>
       </c>
       <c r="R17" t="n">
-        <v>7211612</v>
+        <v>7211717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,32 +2395,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B18" t="n">
-        <v>80121</v>
+        <v>58522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R18" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288412</v>
+        <v>127288436</v>
       </c>
       <c r="B19" t="n">
-        <v>58520</v>
+        <v>80123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753218</v>
+        <v>753266</v>
       </c>
       <c r="R19" t="n">
-        <v>7211643</v>
+        <v>7211612</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288458</v>
+        <v>127288430</v>
       </c>
       <c r="B20" t="n">
-        <v>75134</v>
+        <v>80123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753233</v>
+        <v>753188</v>
       </c>
       <c r="R20" t="n">
-        <v>7211574</v>
+        <v>7211856</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288447</v>
+        <v>127288448</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         <v>753191</v>
       </c>
       <c r="R24" t="n">
-        <v>7211761</v>
+        <v>7211707</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288448</v>
+        <v>127288432</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753191</v>
+        <v>753324</v>
       </c>
       <c r="R25" t="n">
-        <v>7211707</v>
+        <v>7211590</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,11 +3150,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3181,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288432</v>
+        <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3192,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3216,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R26" t="n">
-        <v>7211590</v>
+        <v>7211761</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3252,6 +3247,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,7 +3281,7 @@
         <v>127288434</v>
       </c>
       <c r="B27" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>127288442</v>
       </c>
       <c r="B31" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>127288453</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,7 +4167,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288443</v>
+        <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>91348</v>
+        <v>57663</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4466,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753011</v>
+        <v>753247</v>
       </c>
       <c r="R39" t="n">
-        <v>7211692</v>
+        <v>7211655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4534,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,10 +4565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288445</v>
+        <v>127288443</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,21 +4576,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4587,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753220</v>
+        <v>753011</v>
       </c>
       <c r="R40" t="n">
-        <v>7211637</v>
+        <v>7211692</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4649,10 +4662,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B41" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,42 +4673,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R41" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,11 +4733,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127288450</v>
+        <v>127288433</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>80123</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,21 +4770,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753255</v>
+        <v>753330</v>
       </c>
       <c r="R42" t="n">
-        <v>7211635</v>
+        <v>7211606</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127288433</v>
+        <v>127288450</v>
       </c>
       <c r="B43" t="n">
-        <v>80121</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753330</v>
+        <v>753255</v>
       </c>
       <c r="R43" t="n">
-        <v>7211606</v>
+        <v>7211635</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4956,7 +4956,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80156</v>
+        <v>80158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288458</v>
+        <v>127288449</v>
       </c>
       <c r="B16" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753233</v>
+        <v>753175</v>
       </c>
       <c r="R16" t="n">
-        <v>7211574</v>
+        <v>7211717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288449</v>
+        <v>127288436</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753175</v>
+        <v>753266</v>
       </c>
       <c r="R17" t="n">
-        <v>7211717</v>
+        <v>7211612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,32 +2395,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288412</v>
+        <v>127288430</v>
       </c>
       <c r="B18" t="n">
-        <v>58522</v>
+        <v>80123</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753218</v>
+        <v>753188</v>
       </c>
       <c r="R18" t="n">
-        <v>7211643</v>
+        <v>7211856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>80123</v>
+        <v>75136</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R19" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>80123</v>
+        <v>58522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R20" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>80158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R22" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B23" t="n">
-        <v>80158</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R23" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288448</v>
+        <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753191</v>
+        <v>753284</v>
       </c>
       <c r="R24" t="n">
-        <v>7211707</v>
+        <v>7211602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,11 +3048,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288432</v>
+        <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3085,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3109,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R25" t="n">
-        <v>7211590</v>
+        <v>7211707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3145,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3278,7 +3278,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288434</v>
+        <v>127288432</v>
       </c>
       <c r="B27" t="n">
         <v>80123</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753345</v>
+        <v>753324</v>
       </c>
       <c r="R27" t="n">
-        <v>7211616</v>
+        <v>7211590</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288438</v>
+        <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753284</v>
+        <v>753345</v>
       </c>
       <c r="R28" t="n">
-        <v>7211602</v>
+        <v>7211616</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,53 +3472,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288422</v>
+        <v>127288425</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>98471</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753107</v>
+        <v>753269</v>
       </c>
       <c r="R29" t="n">
-        <v>7211679</v>
+        <v>7211606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,11 +3543,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,45 +3569,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288425</v>
+        <v>127288422</v>
       </c>
       <c r="B30" t="n">
-        <v>98471</v>
+        <v>57823</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753269</v>
+        <v>753107</v>
       </c>
       <c r="R30" t="n">
-        <v>7211606</v>
+        <v>7211679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,6 +3648,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288451</v>
+        <v>127288441</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753241</v>
+        <v>753235</v>
       </c>
       <c r="R34" t="n">
-        <v>7211651</v>
+        <v>7211650</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288431</v>
+        <v>127288451</v>
       </c>
       <c r="B35" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753300</v>
+        <v>753241</v>
       </c>
       <c r="R35" t="n">
-        <v>7211568</v>
+        <v>7211651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288441</v>
+        <v>127288431</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753235</v>
+        <v>753300</v>
       </c>
       <c r="R36" t="n">
-        <v>7211650</v>
+        <v>7211568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288415</v>
+        <v>127288443</v>
       </c>
       <c r="B39" t="n">
-        <v>57663</v>
+        <v>91350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,42 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753247</v>
+        <v>753011</v>
       </c>
       <c r="R39" t="n">
-        <v>7211655</v>
+        <v>7211692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4534,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4565,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288443</v>
+        <v>127288415</v>
       </c>
       <c r="B40" t="n">
-        <v>91350</v>
+        <v>57663</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4576,34 +4563,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753011</v>
+        <v>753247</v>
       </c>
       <c r="R40" t="n">
-        <v>7211692</v>
+        <v>7211655</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4636,6 +4631,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127288433</v>
+        <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>80123</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,21 +4770,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753330</v>
+        <v>753255</v>
       </c>
       <c r="R42" t="n">
-        <v>7211606</v>
+        <v>7211635</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127288450</v>
+        <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753255</v>
+        <v>753330</v>
       </c>
       <c r="R43" t="n">
-        <v>7211635</v>
+        <v>7211606</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5063,45 +5063,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B45" t="n">
-        <v>80158</v>
+        <v>57663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R45" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5134,6 +5142,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5160,53 +5173,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B46" t="n">
-        <v>57663</v>
+        <v>80158</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R46" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,11 +5244,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2201,32 +2201,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288449</v>
+        <v>127288412</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>58522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753175</v>
+        <v>753218</v>
       </c>
       <c r="R16" t="n">
-        <v>7211717</v>
+        <v>7211643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B17" t="n">
-        <v>80123</v>
+        <v>75136</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R17" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,7 +2395,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288430</v>
+        <v>127288436</v>
       </c>
       <c r="B18" t="n">
         <v>80123</v>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753188</v>
+        <v>753266</v>
       </c>
       <c r="R18" t="n">
-        <v>7211856</v>
+        <v>7211612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288458</v>
+        <v>127288430</v>
       </c>
       <c r="B19" t="n">
-        <v>75136</v>
+        <v>80123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753233</v>
+        <v>753188</v>
       </c>
       <c r="R19" t="n">
-        <v>7211574</v>
+        <v>7211856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288412</v>
+        <v>127288449</v>
       </c>
       <c r="B20" t="n">
-        <v>58522</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753218</v>
+        <v>753175</v>
       </c>
       <c r="R20" t="n">
-        <v>7211643</v>
+        <v>7211717</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>80158</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R22" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>80158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R23" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1897,45 +1897,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>80158</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R13" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,6 +1976,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>57663</v>
+        <v>80158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R14" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,11 +2078,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,32 +2201,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288412</v>
+        <v>127288449</v>
       </c>
       <c r="B16" t="n">
-        <v>58522</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753218</v>
+        <v>753175</v>
       </c>
       <c r="R16" t="n">
-        <v>7211643</v>
+        <v>7211717</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288449</v>
+        <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>58522</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753175</v>
+        <v>753218</v>
       </c>
       <c r="R20" t="n">
-        <v>7211717</v>
+        <v>7211643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3074,7 +3074,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288448</v>
+        <v>127288447</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3112,7 +3112,7 @@
         <v>753191</v>
       </c>
       <c r="R25" t="n">
-        <v>7211707</v>
+        <v>7211761</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288447</v>
+        <v>127288448</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3214,7 +3214,7 @@
         <v>753191</v>
       </c>
       <c r="R26" t="n">
-        <v>7211761</v>
+        <v>7211707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3472,45 +3472,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288425</v>
+        <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>98471</v>
+        <v>57823</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753269</v>
+        <v>753107</v>
       </c>
       <c r="R29" t="n">
-        <v>7211606</v>
+        <v>7211679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,6 +3551,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,53 +3582,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288422</v>
+        <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>57823</v>
+        <v>98471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753107</v>
+        <v>753269</v>
       </c>
       <c r="R30" t="n">
-        <v>7211679</v>
+        <v>7211606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,11 +3653,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R31" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>98450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R32" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,42 +4563,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R40" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,11 +4623,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4662,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4673,34 +4660,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R41" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4733,6 +4728,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,32 +2201,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288449</v>
+        <v>127288412</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>58522</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753175</v>
+        <v>753218</v>
       </c>
       <c r="R16" t="n">
-        <v>7211717</v>
+        <v>7211643</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288458</v>
+        <v>127288449</v>
       </c>
       <c r="B17" t="n">
-        <v>75136</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753233</v>
+        <v>753175</v>
       </c>
       <c r="R17" t="n">
-        <v>7211574</v>
+        <v>7211717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B18" t="n">
-        <v>80123</v>
+        <v>75136</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R18" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,7 +2492,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288430</v>
+        <v>127288436</v>
       </c>
       <c r="B19" t="n">
         <v>80123</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753188</v>
+        <v>753266</v>
       </c>
       <c r="R19" t="n">
-        <v>7211856</v>
+        <v>7211612</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288412</v>
+        <v>127288430</v>
       </c>
       <c r="B20" t="n">
-        <v>58522</v>
+        <v>80123</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753218</v>
+        <v>753188</v>
       </c>
       <c r="R20" t="n">
-        <v>7211643</v>
+        <v>7211856</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288438</v>
+        <v>127288447</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753284</v>
+        <v>753191</v>
       </c>
       <c r="R24" t="n">
-        <v>7211602</v>
+        <v>7211761</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,6 +3048,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,7 +3079,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288447</v>
+        <v>127288448</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -3112,7 +3117,7 @@
         <v>753191</v>
       </c>
       <c r="R25" t="n">
-        <v>7211761</v>
+        <v>7211707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3176,10 +3181,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288448</v>
+        <v>127288432</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>80123</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3192,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753191</v>
+        <v>753324</v>
       </c>
       <c r="R26" t="n">
-        <v>7211707</v>
+        <v>7211590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,11 +3252,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3278,7 +3278,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288432</v>
+        <v>127288434</v>
       </c>
       <c r="B27" t="n">
         <v>80123</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753324</v>
+        <v>753345</v>
       </c>
       <c r="R27" t="n">
-        <v>7211590</v>
+        <v>7211616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288434</v>
+        <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753345</v>
+        <v>753284</v>
       </c>
       <c r="R28" t="n">
-        <v>7211616</v>
+        <v>7211602</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288441</v>
+        <v>127288431</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>80123</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753235</v>
+        <v>753300</v>
       </c>
       <c r="R34" t="n">
-        <v>7211650</v>
+        <v>7211568</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288431</v>
+        <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>80123</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753300</v>
+        <v>753235</v>
       </c>
       <c r="R36" t="n">
-        <v>7211568</v>
+        <v>7211650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4458,7 +4458,7 @@
         <v>127288443</v>
       </c>
       <c r="B39" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,53 +1897,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>80161</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R13" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B14" t="n">
-        <v>80158</v>
+        <v>57666</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R14" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,6 +2073,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>127288412</v>
       </c>
       <c r="B16" t="n">
-        <v>58522</v>
+        <v>58525</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288449</v>
+        <v>127288458</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>75139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753175</v>
+        <v>753233</v>
       </c>
       <c r="R17" t="n">
-        <v>7211717</v>
+        <v>7211574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288458</v>
+        <v>127288436</v>
       </c>
       <c r="B18" t="n">
-        <v>75136</v>
+        <v>80126</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753233</v>
+        <v>753266</v>
       </c>
       <c r="R18" t="n">
-        <v>7211574</v>
+        <v>7211612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288436</v>
+        <v>127288449</v>
       </c>
       <c r="B19" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753266</v>
+        <v>753175</v>
       </c>
       <c r="R19" t="n">
-        <v>7211612</v>
+        <v>7211717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2592,7 @@
         <v>127288430</v>
       </c>
       <c r="B20" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>80161</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R22" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B23" t="n">
-        <v>80158</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R23" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2980,7 +2980,7 @@
         <v>127288447</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288448</v>
+        <v>127288432</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753191</v>
+        <v>753324</v>
       </c>
       <c r="R25" t="n">
-        <v>7211707</v>
+        <v>7211590</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,11 +3150,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3181,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288432</v>
+        <v>127288448</v>
       </c>
       <c r="B26" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3192,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3216,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R26" t="n">
-        <v>7211590</v>
+        <v>7211707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3252,6 +3247,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3281,7 +3281,7 @@
         <v>127288434</v>
       </c>
       <c r="B27" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288431</v>
+        <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753300</v>
+        <v>753241</v>
       </c>
       <c r="R34" t="n">
-        <v>7211568</v>
+        <v>7211651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,32 +4067,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288451</v>
+        <v>127288441</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753241</v>
+        <v>753235</v>
       </c>
       <c r="R35" t="n">
-        <v>7211651</v>
+        <v>7211650</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288441</v>
+        <v>127288431</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>80126</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753235</v>
+        <v>753300</v>
       </c>
       <c r="R36" t="n">
-        <v>7211650</v>
+        <v>7211568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>127288443</v>
       </c>
       <c r="B39" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>127288415</v>
       </c>
       <c r="B41" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127288450</v>
+        <v>127288433</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>80126</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,21 +4770,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753255</v>
+        <v>753330</v>
       </c>
       <c r="R42" t="n">
-        <v>7211635</v>
+        <v>7211606</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127288433</v>
+        <v>127288450</v>
       </c>
       <c r="B43" t="n">
-        <v>80123</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753330</v>
+        <v>753255</v>
       </c>
       <c r="R43" t="n">
-        <v>7211606</v>
+        <v>7211635</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4956,7 +4956,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>127288417</v>
       </c>
       <c r="B45" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>127288455</v>
       </c>
       <c r="B46" t="n">
-        <v>80158</v>
+        <v>80161</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1900,7 +1900,7 @@
         <v>127288456</v>
       </c>
       <c r="B13" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>127288418</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,32 +2201,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288412</v>
+        <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>58525</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753218</v>
+        <v>753266</v>
       </c>
       <c r="R16" t="n">
-        <v>7211643</v>
+        <v>7211612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288458</v>
+        <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>75139</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753233</v>
+        <v>753188</v>
       </c>
       <c r="R17" t="n">
-        <v>7211574</v>
+        <v>7211856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288436</v>
+        <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>80126</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753266</v>
+        <v>753175</v>
       </c>
       <c r="R18" t="n">
-        <v>7211612</v>
+        <v>7211717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288449</v>
+        <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>75145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753175</v>
+        <v>753233</v>
       </c>
       <c r="R19" t="n">
-        <v>7211717</v>
+        <v>7211574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>80126</v>
+        <v>58531</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R20" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>80161</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R22" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>80167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R23" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288447</v>
+        <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753191</v>
+        <v>753284</v>
       </c>
       <c r="R24" t="n">
-        <v>7211761</v>
+        <v>7211602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,11 +3048,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288432</v>
+        <v>127288434</v>
       </c>
       <c r="B25" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3114,10 +3109,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753324</v>
+        <v>753345</v>
       </c>
       <c r="R25" t="n">
-        <v>7211590</v>
+        <v>7211616</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3179,7 +3174,7 @@
         <v>127288448</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288434</v>
+        <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3313,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753345</v>
+        <v>753324</v>
       </c>
       <c r="R27" t="n">
-        <v>7211616</v>
+        <v>7211590</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,32 +3370,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288438</v>
+        <v>127288447</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753284</v>
+        <v>753191</v>
       </c>
       <c r="R28" t="n">
-        <v>7211602</v>
+        <v>7211761</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3446,6 +3441,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3475,7 +3475,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98480</v>
+        <v>98488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4067,32 +4067,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288441</v>
+        <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>98459</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753235</v>
+        <v>753300</v>
       </c>
       <c r="R35" t="n">
-        <v>7211650</v>
+        <v>7211568</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288431</v>
+        <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>80126</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753300</v>
+        <v>753235</v>
       </c>
       <c r="R36" t="n">
-        <v>7211568</v>
+        <v>7211650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288443</v>
+        <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>91359</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4466,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753011</v>
+        <v>753247</v>
       </c>
       <c r="R39" t="n">
-        <v>7211692</v>
+        <v>7211655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4534,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4555,7 +4568,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4649,10 +4662,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288415</v>
+        <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>57666</v>
+        <v>91367</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,42 +4673,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753247</v>
+        <v>753011</v>
       </c>
       <c r="R41" t="n">
-        <v>7211655</v>
+        <v>7211692</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,11 +4733,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4762,7 +4762,7 @@
         <v>127288433</v>
       </c>
       <c r="B42" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4859,7 +4859,7 @@
         <v>127288450</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>127288417</v>
       </c>
       <c r="B45" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>127288455</v>
       </c>
       <c r="B46" t="n">
-        <v>80161</v>
+        <v>80167</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>75145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R16" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288430</v>
+        <v>127288436</v>
       </c>
       <c r="B17" t="n">
         <v>80132</v>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753188</v>
+        <v>753266</v>
       </c>
       <c r="R17" t="n">
-        <v>7211856</v>
+        <v>7211612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R18" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288458</v>
+        <v>127288449</v>
       </c>
       <c r="B19" t="n">
-        <v>75145</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753233</v>
+        <v>753175</v>
       </c>
       <c r="R19" t="n">
-        <v>7211574</v>
+        <v>7211717</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R22" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B23" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R23" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288438</v>
+        <v>127288447</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753284</v>
+        <v>753191</v>
       </c>
       <c r="R24" t="n">
-        <v>7211602</v>
+        <v>7211761</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,6 +3048,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,7 +3079,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288434</v>
+        <v>127288432</v>
       </c>
       <c r="B25" t="n">
         <v>80132</v>
@@ -3109,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753345</v>
+        <v>753324</v>
       </c>
       <c r="R25" t="n">
-        <v>7211616</v>
+        <v>7211590</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3273,7 +3278,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288432</v>
+        <v>127288434</v>
       </c>
       <c r="B27" t="n">
         <v>80132</v>
@@ -3308,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753324</v>
+        <v>753345</v>
       </c>
       <c r="R27" t="n">
-        <v>7211590</v>
+        <v>7211616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3370,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288447</v>
+        <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3405,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753191</v>
+        <v>753284</v>
       </c>
       <c r="R28" t="n">
-        <v>7211761</v>
+        <v>7211602</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3441,11 +3446,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,7 +3585,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98488</v>
+        <v>98489</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,10 +3970,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288451</v>
+        <v>127288431</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753241</v>
+        <v>753300</v>
       </c>
       <c r="R34" t="n">
-        <v>7211651</v>
+        <v>7211568</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288431</v>
+        <v>127288451</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753300</v>
+        <v>753241</v>
       </c>
       <c r="R35" t="n">
-        <v>7211568</v>
+        <v>7211651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4167,7 +4167,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,42 +4466,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R39" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4534,11 +4526,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4565,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4576,34 +4563,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R40" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4636,6 +4631,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4665,7 +4665,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5063,53 +5063,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R45" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,11 +5134,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,45 +5160,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R46" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,6 +5239,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288430</v>
+        <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753188</v>
+        <v>753175</v>
       </c>
       <c r="R18" t="n">
-        <v>7211856</v>
+        <v>7211717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R19" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288447</v>
+        <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753191</v>
+        <v>753284</v>
       </c>
       <c r="R24" t="n">
-        <v>7211761</v>
+        <v>7211602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,11 +3048,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288432</v>
+        <v>127288447</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3085,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3109,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R25" t="n">
-        <v>7211590</v>
+        <v>7211761</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3145,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288448</v>
+        <v>127288432</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753191</v>
+        <v>753324</v>
       </c>
       <c r="R26" t="n">
-        <v>7211707</v>
+        <v>7211590</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,11 +3247,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3278,10 +3273,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288434</v>
+        <v>127288448</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3284,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3308,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753345</v>
+        <v>753191</v>
       </c>
       <c r="R27" t="n">
-        <v>7211616</v>
+        <v>7211707</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,6 +3344,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288438</v>
+        <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753284</v>
+        <v>753345</v>
       </c>
       <c r="R28" t="n">
-        <v>7211602</v>
+        <v>7211616</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R31" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R32" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3970,10 +3970,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288431</v>
+        <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3981,21 +3981,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753300</v>
+        <v>753241</v>
       </c>
       <c r="R34" t="n">
-        <v>7211568</v>
+        <v>7211651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288451</v>
+        <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753241</v>
+        <v>753300</v>
       </c>
       <c r="R35" t="n">
-        <v>7211651</v>
+        <v>7211568</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288445</v>
+        <v>127288443</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>91368</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,21 +4466,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753220</v>
+        <v>753011</v>
       </c>
       <c r="R39" t="n">
-        <v>7211637</v>
+        <v>7211692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,42 +4563,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R40" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,11 +4623,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4662,10 +4649,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288443</v>
+        <v>127288415</v>
       </c>
       <c r="B41" t="n">
-        <v>91368</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4673,34 +4660,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753011</v>
+        <v>753247</v>
       </c>
       <c r="R41" t="n">
-        <v>7211692</v>
+        <v>7211655</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4733,6 +4728,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1897,45 +1897,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R13" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,6 +1976,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R14" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,11 +2078,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288458</v>
+        <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>75145</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753233</v>
+        <v>753266</v>
       </c>
       <c r="R16" t="n">
-        <v>7211574</v>
+        <v>7211612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288436</v>
+        <v>127288449</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753266</v>
+        <v>753175</v>
       </c>
       <c r="R17" t="n">
-        <v>7211612</v>
+        <v>7211717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R18" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288430</v>
+        <v>127288412</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>58531</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753188</v>
+        <v>753218</v>
       </c>
       <c r="R19" t="n">
-        <v>7211856</v>
+        <v>7211643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288412</v>
+        <v>127288458</v>
       </c>
       <c r="B20" t="n">
-        <v>58531</v>
+        <v>75145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208249</v>
+        <v>308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753218</v>
+        <v>753233</v>
       </c>
       <c r="R20" t="n">
-        <v>7211643</v>
+        <v>7211574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98489</v>
+        <v>98490</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288438</v>
+        <v>127288447</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753284</v>
+        <v>753191</v>
       </c>
       <c r="R24" t="n">
-        <v>7211602</v>
+        <v>7211761</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,6 +3048,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3074,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288447</v>
+        <v>127288432</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3085,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3109,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753191</v>
+        <v>753324</v>
       </c>
       <c r="R25" t="n">
-        <v>7211761</v>
+        <v>7211590</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3145,11 +3150,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,10 +3176,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288432</v>
+        <v>127288448</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,21 +3187,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R26" t="n">
-        <v>7211590</v>
+        <v>7211707</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3247,6 +3247,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3273,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288448</v>
+        <v>127288434</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3284,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3308,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753191</v>
+        <v>753345</v>
       </c>
       <c r="R27" t="n">
-        <v>7211707</v>
+        <v>7211616</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3344,11 +3349,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3375,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288434</v>
+        <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>98469</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753345</v>
+        <v>753284</v>
       </c>
       <c r="R28" t="n">
-        <v>7211616</v>
+        <v>7211602</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3472,53 +3472,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288422</v>
+        <v>127288425</v>
       </c>
       <c r="B29" t="n">
-        <v>57832</v>
+        <v>98490</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753107</v>
+        <v>753269</v>
       </c>
       <c r="R29" t="n">
-        <v>7211679</v>
+        <v>7211606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3551,11 +3543,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3582,45 +3569,53 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288425</v>
+        <v>127288422</v>
       </c>
       <c r="B30" t="n">
-        <v>98489</v>
+        <v>57832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753269</v>
+        <v>753107</v>
       </c>
       <c r="R30" t="n">
-        <v>7211606</v>
+        <v>7211679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3653,6 +3648,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3679,32 +3679,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288442</v>
+        <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753219</v>
+        <v>753179</v>
       </c>
       <c r="R31" t="n">
-        <v>7211658</v>
+        <v>7211888</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3776,32 +3776,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288453</v>
+        <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3811,10 +3811,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753179</v>
+        <v>753219</v>
       </c>
       <c r="R32" t="n">
-        <v>7211888</v>
+        <v>7211658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288451</v>
+        <v>127288441</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753241</v>
+        <v>753235</v>
       </c>
       <c r="R34" t="n">
-        <v>7211651</v>
+        <v>7211650</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288431</v>
+        <v>127288451</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753300</v>
+        <v>753241</v>
       </c>
       <c r="R35" t="n">
-        <v>7211568</v>
+        <v>7211651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288441</v>
+        <v>127288431</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753235</v>
+        <v>753300</v>
       </c>
       <c r="R36" t="n">
-        <v>7211650</v>
+        <v>7211568</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288443</v>
+        <v>127288445</v>
       </c>
       <c r="B39" t="n">
-        <v>91368</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,21 +4466,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4490,10 +4490,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753011</v>
+        <v>753220</v>
       </c>
       <c r="R39" t="n">
-        <v>7211692</v>
+        <v>7211637</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4552,10 +4552,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,34 +4563,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R40" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4623,6 +4631,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4649,10 +4662,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288415</v>
+        <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>91369</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4660,42 +4673,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753247</v>
+        <v>753011</v>
       </c>
       <c r="R41" t="n">
-        <v>7211655</v>
+        <v>7211692</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,11 +4733,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5063,45 +5063,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B45" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R45" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5134,6 +5142,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5160,53 +5173,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R46" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,11 +5244,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1897,53 +1897,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R13" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1976,11 +1968,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,45 +1994,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B14" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R14" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2078,6 +2073,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,7 +2107,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288436</v>
+        <v>127288458</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>75145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753266</v>
+        <v>753233</v>
       </c>
       <c r="R16" t="n">
-        <v>7211612</v>
+        <v>7211574</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288449</v>
+        <v>127288436</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753175</v>
+        <v>753266</v>
       </c>
       <c r="R17" t="n">
-        <v>7211717</v>
+        <v>7211612</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288430</v>
+        <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753188</v>
+        <v>753175</v>
       </c>
       <c r="R18" t="n">
-        <v>7211856</v>
+        <v>7211717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,32 +2492,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288412</v>
+        <v>127288430</v>
       </c>
       <c r="B19" t="n">
-        <v>58531</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753218</v>
+        <v>753188</v>
       </c>
       <c r="R19" t="n">
-        <v>7211643</v>
+        <v>7211856</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2589,32 +2589,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288458</v>
+        <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>75145</v>
+        <v>58531</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>308</v>
+        <v>208249</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753233</v>
+        <v>753218</v>
       </c>
       <c r="R20" t="n">
-        <v>7211574</v>
+        <v>7211643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2689,7 +2689,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288457</v>
+        <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>80167</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753330</v>
+        <v>753279</v>
       </c>
       <c r="R22" t="n">
-        <v>7211606</v>
+        <v>7211533</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2880,27 +2880,27 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288444</v>
+        <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>80167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753279</v>
+        <v>753330</v>
       </c>
       <c r="R23" t="n">
-        <v>7211533</v>
+        <v>7211606</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3378,7 +3378,7 @@
         <v>127288438</v>
       </c>
       <c r="B28" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3472,45 +3472,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288425</v>
+        <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>98490</v>
+        <v>57832</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753269</v>
+        <v>753107</v>
       </c>
       <c r="R29" t="n">
-        <v>7211606</v>
+        <v>7211679</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3543,6 +3551,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3569,53 +3582,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288422</v>
+        <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>57832</v>
+        <v>98491</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753107</v>
+        <v>753269</v>
       </c>
       <c r="R30" t="n">
-        <v>7211679</v>
+        <v>7211606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3648,11 +3653,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Lock</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3779,7 +3779,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3876,7 +3876,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3970,32 +3970,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288441</v>
+        <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753235</v>
+        <v>753241</v>
       </c>
       <c r="R34" t="n">
-        <v>7211650</v>
+        <v>7211651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288451</v>
+        <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753241</v>
+        <v>753300</v>
       </c>
       <c r="R35" t="n">
-        <v>7211651</v>
+        <v>7211568</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,32 +4164,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288431</v>
+        <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753300</v>
+        <v>753235</v>
       </c>
       <c r="R36" t="n">
-        <v>7211568</v>
+        <v>7211650</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4665,7 +4665,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5063,53 +5063,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288417</v>
+        <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753086</v>
+        <v>753192</v>
       </c>
       <c r="R45" t="n">
-        <v>7211788</v>
+        <v>7211856</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,11 +5134,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,45 +5160,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288455</v>
+        <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753192</v>
+        <v>753086</v>
       </c>
       <c r="R46" t="n">
-        <v>7211856</v>
+        <v>7211788</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,6 +5239,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1897,45 +1897,53 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288456</v>
+        <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>80167</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753189</v>
+        <v>753102</v>
       </c>
       <c r="R13" t="n">
-        <v>7211853</v>
+        <v>7211838</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,6 +1976,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1994,53 +2007,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288418</v>
+        <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753102</v>
+        <v>753189</v>
       </c>
       <c r="R14" t="n">
-        <v>7211838</v>
+        <v>7211853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,11 +2078,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288436</v>
+        <v>127288449</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753266</v>
+        <v>753175</v>
       </c>
       <c r="R17" t="n">
-        <v>7211612</v>
+        <v>7211717</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288449</v>
+        <v>127288436</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753175</v>
+        <v>753266</v>
       </c>
       <c r="R18" t="n">
-        <v>7211717</v>
+        <v>7211612</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2977,32 +2977,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288447</v>
+        <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753191</v>
+        <v>753284</v>
       </c>
       <c r="R24" t="n">
-        <v>7211761</v>
+        <v>7211602</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3048,11 +3048,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,10 +3074,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288432</v>
+        <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3085,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3109,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753324</v>
+        <v>753191</v>
       </c>
       <c r="R25" t="n">
-        <v>7211590</v>
+        <v>7211707</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3145,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,7 +3176,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288448</v>
+        <v>127288447</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3214,7 +3214,7 @@
         <v>753191</v>
       </c>
       <c r="R26" t="n">
-        <v>7211707</v>
+        <v>7211761</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288434</v>
+        <v>127288432</v>
       </c>
       <c r="B27" t="n">
         <v>80132</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753345</v>
+        <v>753324</v>
       </c>
       <c r="R27" t="n">
-        <v>7211616</v>
+        <v>7211590</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3375,32 +3375,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288438</v>
+        <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3410,10 +3410,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753284</v>
+        <v>753345</v>
       </c>
       <c r="R28" t="n">
-        <v>7211602</v>
+        <v>7211616</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288445</v>
+        <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4466,34 +4466,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753220</v>
+        <v>753247</v>
       </c>
       <c r="R39" t="n">
-        <v>7211637</v>
+        <v>7211655</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4526,6 +4534,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4552,10 +4565,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288415</v>
+        <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4563,42 +4576,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753247</v>
+        <v>753220</v>
       </c>
       <c r="R40" t="n">
-        <v>7211655</v>
+        <v>7211637</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4631,11 +4636,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4759,10 +4759,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127288433</v>
+        <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4770,21 +4770,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753330</v>
+        <v>753255</v>
       </c>
       <c r="R42" t="n">
-        <v>7211606</v>
+        <v>7211635</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,10 +4856,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127288450</v>
+        <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4867,21 +4867,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4891,10 +4891,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753255</v>
+        <v>753330</v>
       </c>
       <c r="R43" t="n">
-        <v>7211635</v>
+        <v>7211606</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2201,10 +2201,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288458</v>
+        <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>75145</v>
+        <v>80132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753233</v>
+        <v>753266</v>
       </c>
       <c r="R16" t="n">
-        <v>7211574</v>
+        <v>7211612</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,10 +2298,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288449</v>
+        <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>80132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,21 +2309,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2333,10 +2333,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753175</v>
+        <v>753188</v>
       </c>
       <c r="R17" t="n">
-        <v>7211717</v>
+        <v>7211856</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2395,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288436</v>
+        <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>80132</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753266</v>
+        <v>753175</v>
       </c>
       <c r="R18" t="n">
-        <v>7211612</v>
+        <v>7211717</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288430</v>
+        <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>75145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753188</v>
+        <v>753233</v>
       </c>
       <c r="R19" t="n">
-        <v>7211856</v>
+        <v>7211574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5268,6 +5268,112 @@
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128533114</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kankberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>753134</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7211650</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5273,7 +5273,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91352</v>
+        <v>91504</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,14 +1673,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,14 +1787,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1893,14 +1901,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2003,14 +2015,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80167</v>
+        <v>80260</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2100,14 +2116,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,14 +2217,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2294,14 +2318,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2391,14 +2419,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2488,14 +2520,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>75145</v>
+        <v>75197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,14 +2621,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>58531</v>
+        <v>58575</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,14 +2722,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98491</v>
+        <v>98653</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2779,14 +2823,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2876,14 +2924,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80167</v>
+        <v>80260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2973,14 +3025,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3070,14 +3126,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,14 +3232,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,14 +3338,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3371,14 +3439,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3468,14 +3540,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57832</v>
+        <v>57876</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3578,14 +3654,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98491</v>
+        <v>98653</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3675,14 +3755,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3772,14 +3856,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY31" t="inlineStr"/>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3869,14 +3957,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3966,14 +4058,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr"/>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4063,14 +4159,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4160,14 +4260,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4257,14 +4361,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY36" t="inlineStr"/>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80161</v>
+        <v>80254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4354,14 +4462,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4451,14 +4563,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY38" t="inlineStr"/>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4561,14 +4677,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4658,14 +4778,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91370</v>
+        <v>91522</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4755,14 +4879,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY41" t="inlineStr"/>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79120</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4852,14 +4980,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr"/>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80132</v>
+        <v>80225</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4949,14 +5081,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr"/>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5059,14 +5195,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr"/>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80167</v>
+        <v>80260</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5156,14 +5296,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>57716</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5266,7 +5410,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>58575</v>
+        <v>58579</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>58579</v>
+        <v>58582</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -5421,7 +5421,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98672</v>
+        <v>98677</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98677</v>
+        <v>98680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>128533114</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>58582</v>
+        <v>58584</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98680</v>
+        <v>98690</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80169</v>
+        <v>80173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98690</v>
+        <v>98697</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>127288416</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>127288414</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>127288418</v>
       </c>
       <c r="B13" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2632,7 +2632,7 @@
         <v>127288412</v>
       </c>
       <c r="B20" t="n">
-        <v>58584</v>
+        <v>58586</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>127288422</v>
       </c>
       <c r="B29" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98697</v>
+        <v>98699</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80173</v>
+        <v>80175</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>127288415</v>
       </c>
       <c r="B39" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5092,7 +5092,7 @@
         <v>127288419</v>
       </c>
       <c r="B44" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5206,7 +5206,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80179</v>
+        <v>80181</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         <v>127288417</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98699</v>
+        <v>98725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98725</v>
+        <v>98726</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4806,14 +4806,10 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98726</v>
+        <v>98727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>82999</v>
+        <v>83003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98727</v>
+        <v>98731</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80175</v>
+        <v>80177</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80181</v>
+        <v>80183</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2026,7 +2026,7 @@
         <v>127288456</v>
       </c>
       <c r="B14" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>127288436</v>
       </c>
       <c r="B16" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         <v>127288430</v>
       </c>
       <c r="B17" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>127288449</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>127288458</v>
       </c>
       <c r="B19" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         <v>127288444</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>127288457</v>
       </c>
       <c r="B23" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>127288448</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>127288447</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>127288432</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>127288434</v>
       </c>
       <c r="B28" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98731</v>
+        <v>98733</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>127288453</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>127288451</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>127288431</v>
       </c>
       <c r="B35" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>127288423</v>
       </c>
       <c r="B37" t="n">
-        <v>80177</v>
+        <v>80178</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>127288428</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>127288445</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         <v>127288450</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>127288433</v>
       </c>
       <c r="B43" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v>127288455</v>
       </c>
       <c r="B45" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -1583,7 +1583,7 @@
         <v>127288413</v>
       </c>
       <c r="B10" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         <v>127288440</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         <v>127288424</v>
       </c>
       <c r="B21" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>127288438</v>
       </c>
       <c r="B24" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>127288425</v>
       </c>
       <c r="B30" t="n">
-        <v>98733</v>
+        <v>98737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>127288442</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>127288439</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>127288441</v>
       </c>
       <c r="B36" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4789,7 +4789,7 @@
         <v>127288443</v>
       </c>
       <c r="B41" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106229116</v>
+        <v>127288458</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>753207.1783706248</v>
+        <v>753233</v>
       </c>
       <c r="R2" t="n">
-        <v>7211839.627265311</v>
+        <v>7211574</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,76 +754,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106229099</v>
+        <v>111966181</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Röjmyrbrännet, Vb</t>
+          <t>Röjmyrbrännet, Kankberg, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>753189.8922463949</v>
+        <v>753190</v>
       </c>
       <c r="R3" t="n">
-        <v>7211857.328302954</v>
+        <v>7211856</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,34 +855,32 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111966178</v>
+        <v>111966177</v>
       </c>
       <c r="B4" t="n">
-        <v>89938</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,16 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -954,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>753214</v>
+        <v>753234</v>
       </c>
       <c r="R4" t="n">
-        <v>7211704</v>
+        <v>7211665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1035,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111966177</v>
+        <v>127288413</v>
       </c>
       <c r="B5" t="n">
-        <v>89553</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,14 +1024,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Röjmyrbrännet, Kankberg, Vb</t>
+          <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>753234</v>
+        <v>753205</v>
       </c>
       <c r="R5" t="n">
-        <v>7211665</v>
+        <v>7211601</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,12 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,85 +1074,65 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111966182</v>
+        <v>127288454</v>
       </c>
       <c r="B6" t="n">
-        <v>78746</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Röjmyrbrännet, Kankberg, Vb</t>
+          <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>753196</v>
+        <v>753170</v>
       </c>
       <c r="R6" t="n">
-        <v>7211857</v>
+        <v>7211911</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,12 +1159,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,53 +1179,48 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111966181</v>
+        <v>111966180</v>
       </c>
       <c r="B7" t="n">
-        <v>90113</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>4404</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1302,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>753190</v>
+        <v>753180</v>
       </c>
       <c r="R7" t="n">
-        <v>7211856</v>
+        <v>7211863</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,19 +1296,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111966179</v>
+        <v>106229116</v>
       </c>
       <c r="B8" t="n">
-        <v>77650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1402,16 +1325,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Röjmyrbrännet, Kankberg, Vb</t>
+          <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>753210</v>
+        <v>753207</v>
       </c>
       <c r="R8" t="n">
-        <v>7211827</v>
+        <v>7211840</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,12 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,59 +1386,51 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111966183</v>
+        <v>111966179</v>
       </c>
       <c r="B9" t="n">
-        <v>78713</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>753196</v>
+        <v>753210</v>
       </c>
       <c r="R9" t="n">
-        <v>7211857</v>
+        <v>7211826</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,32 +1506,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127288413</v>
+        <v>127288444</v>
       </c>
       <c r="B10" t="n">
-        <v>91549</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1615,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>753205</v>
+        <v>753279</v>
       </c>
       <c r="R10" t="n">
-        <v>7211601</v>
+        <v>7211533</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,53 +1607,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127288416</v>
+        <v>127288445</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>753107</v>
+        <v>753220</v>
       </c>
       <c r="R11" t="n">
-        <v>7211679</v>
+        <v>7211637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,11 +1678,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,53 +1708,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127288414</v>
+        <v>127288447</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>753275</v>
+        <v>753191</v>
       </c>
       <c r="R12" t="n">
-        <v>7211522</v>
+        <v>7211761</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,7 +1783,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1909,53 +1814,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127288418</v>
+        <v>127288448</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>753102</v>
+        <v>753191</v>
       </c>
       <c r="R13" t="n">
-        <v>7211838</v>
+        <v>7211707</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,7 +1889,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,27 +1920,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127288456</v>
+        <v>127288449</v>
       </c>
       <c r="B14" t="n">
-        <v>80184</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2058,10 +1955,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>753189</v>
+        <v>753175</v>
       </c>
       <c r="R14" t="n">
-        <v>7211853</v>
+        <v>7211717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127288440</v>
+        <v>127288450</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2135,21 +2032,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2159,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>753266</v>
+        <v>753255</v>
       </c>
       <c r="R15" t="n">
-        <v>7211612</v>
+        <v>7211635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2225,32 +2122,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127288436</v>
+        <v>127288451</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>753266</v>
+        <v>753241</v>
       </c>
       <c r="R16" t="n">
-        <v>7211612</v>
+        <v>7211651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2326,32 +2223,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127288430</v>
+        <v>127288452</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2361,10 +2258,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>753188</v>
+        <v>753082</v>
       </c>
       <c r="R17" t="n">
-        <v>7211856</v>
+        <v>7211739</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2427,14 +2324,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127288449</v>
+        <v>127288453</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2462,10 +2359,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>753175</v>
+        <v>753179</v>
       </c>
       <c r="R18" t="n">
-        <v>7211717</v>
+        <v>7211888</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2528,10 +2425,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127288458</v>
+        <v>106229099</v>
       </c>
       <c r="B19" t="n">
-        <v>83004</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,34 +2436,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>753233</v>
+        <v>753190</v>
       </c>
       <c r="R19" t="n">
-        <v>7211574</v>
+        <v>7211857</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2593,12 +2497,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2019-06-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2607,67 +2511,64 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127288412</v>
+        <v>111966183</v>
       </c>
       <c r="B20" t="n">
-        <v>58586</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208249</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Röjmyrbrännet, Vb</t>
+          <t>Röjmyrbrännet, Kankberg, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>753218</v>
+        <v>753195</v>
       </c>
       <c r="R20" t="n">
-        <v>7211643</v>
+        <v>7211857</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,12 +2595,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2714,48 +2615,48 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127288424</v>
+        <v>127288428</v>
       </c>
       <c r="B21" t="n">
-        <v>98737</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2765,10 +2666,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>753214</v>
+        <v>753286</v>
       </c>
       <c r="R21" t="n">
-        <v>7211833</v>
+        <v>7211540</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2831,10 +2732,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127288444</v>
+        <v>127288430</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2842,21 +2743,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2866,10 +2767,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>753279</v>
+        <v>753188</v>
       </c>
       <c r="R22" t="n">
-        <v>7211533</v>
+        <v>7211856</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2932,32 +2833,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127288457</v>
+        <v>127288431</v>
       </c>
       <c r="B23" t="n">
-        <v>80184</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2967,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>753330</v>
+        <v>753300</v>
       </c>
       <c r="R23" t="n">
-        <v>7211606</v>
+        <v>7211568</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3033,32 +2934,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127288438</v>
+        <v>127288432</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3068,10 +2969,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>753284</v>
+        <v>753324</v>
       </c>
       <c r="R24" t="n">
-        <v>7211602</v>
+        <v>7211590</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3134,10 +3035,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127288448</v>
+        <v>127288433</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3145,21 +3046,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,10 +3070,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>753191</v>
+        <v>753330</v>
       </c>
       <c r="R25" t="n">
-        <v>7211707</v>
+        <v>7211606</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3205,11 +3106,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3240,10 +3136,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127288447</v>
+        <v>127288434</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3251,21 +3147,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3275,10 +3171,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>753191</v>
+        <v>753345</v>
       </c>
       <c r="R26" t="n">
-        <v>7211761</v>
+        <v>7211616</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,11 +3207,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt, långa bålar</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3346,10 +3237,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127288432</v>
+        <v>127288436</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3381,10 +3272,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>753324</v>
+        <v>753266</v>
       </c>
       <c r="R27" t="n">
-        <v>7211590</v>
+        <v>7211612</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3447,32 +3338,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127288434</v>
+        <v>127288423</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80461</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3482,10 +3373,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>753345</v>
+        <v>753266</v>
       </c>
       <c r="R28" t="n">
-        <v>7211616</v>
+        <v>7211612</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3548,53 +3439,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127288422</v>
+        <v>111966182</v>
       </c>
       <c r="B29" t="n">
-        <v>57887</v>
+        <v>80467</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Röjmyrbrännet, Vb</t>
+          <t>Röjmyrbrännet, Kankberg, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>753107</v>
+        <v>753195</v>
       </c>
       <c r="R29" t="n">
-        <v>7211679</v>
+        <v>7211857</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3621,17 +3504,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Lock</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3646,26 +3524,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127288425</v>
+        <v>127288455</v>
       </c>
       <c r="B30" t="n">
-        <v>98737</v>
+        <v>80467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3673,21 +3551,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3697,10 +3575,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>753269</v>
+        <v>753192</v>
       </c>
       <c r="R30" t="n">
-        <v>7211606</v>
+        <v>7211856</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3763,27 +3641,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127288453</v>
+        <v>127288456</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>80467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3798,10 +3676,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>753179</v>
+        <v>753189</v>
       </c>
       <c r="R31" t="n">
-        <v>7211888</v>
+        <v>7211853</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3864,32 +3742,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127288442</v>
+        <v>127288457</v>
       </c>
       <c r="B32" t="n">
-        <v>98716</v>
+        <v>80467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3899,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>753219</v>
+        <v>753330</v>
       </c>
       <c r="R32" t="n">
-        <v>7211658</v>
+        <v>7211606</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3965,45 +3843,53 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127288439</v>
+        <v>127288414</v>
       </c>
       <c r="B33" t="n">
-        <v>98716</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>753269</v>
+        <v>753275</v>
       </c>
       <c r="R33" t="n">
-        <v>7211606</v>
+        <v>7211522</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,6 +3922,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4066,10 +3957,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127288451</v>
+        <v>127288415</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4077,34 +3968,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>753241</v>
+        <v>753247</v>
       </c>
       <c r="R34" t="n">
-        <v>7211651</v>
+        <v>7211655</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4137,6 +4036,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4167,10 +4071,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127288431</v>
+        <v>127288416</v>
       </c>
       <c r="B35" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4178,34 +4082,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>753300</v>
+        <v>753107</v>
       </c>
       <c r="R35" t="n">
-        <v>7211568</v>
+        <v>7211679</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4238,6 +4150,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4268,45 +4185,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127288441</v>
+        <v>127288417</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>753235</v>
+        <v>753086</v>
       </c>
       <c r="R36" t="n">
-        <v>7211650</v>
+        <v>7211788</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4339,6 +4264,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4369,45 +4299,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127288423</v>
+        <v>127288418</v>
       </c>
       <c r="B37" t="n">
-        <v>80178</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>753266</v>
+        <v>753102</v>
       </c>
       <c r="R37" t="n">
-        <v>7211612</v>
+        <v>7211838</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4440,6 +4378,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4470,10 +4413,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127288428</v>
+        <v>127288419</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4481,34 +4424,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>753286</v>
+        <v>753103</v>
       </c>
       <c r="R38" t="n">
-        <v>7211540</v>
+        <v>7211845</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4541,6 +4492,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4571,10 +4527,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127288415</v>
+        <v>127288421</v>
       </c>
       <c r="B39" t="n">
-        <v>57727</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4604,7 +4560,7 @@
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -4614,10 +4570,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>753247</v>
+        <v>753076</v>
       </c>
       <c r="R39" t="n">
-        <v>7211655</v>
+        <v>7211797</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4654,7 +4610,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4685,10 +4641,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127288445</v>
+        <v>127288422</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4696,34 +4652,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>753220</v>
+        <v>753107</v>
       </c>
       <c r="R40" t="n">
-        <v>7211637</v>
+        <v>7211679</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4756,6 +4720,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Lock</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4786,10 +4755,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127288443</v>
+        <v>127288411</v>
       </c>
       <c r="B41" t="n">
-        <v>91569</v>
+        <v>56689</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4797,30 +4766,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>206046</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Alces alces</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>753011</v>
+        <v>753010</v>
       </c>
       <c r="R41" t="n">
-        <v>7211692</v>
+        <v>7211697</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4853,6 +4834,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre spillning</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4883,32 +4869,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127288450</v>
+        <v>127288412</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>58817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>208249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4918,10 +4904,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>753255</v>
+        <v>753218</v>
       </c>
       <c r="R42" t="n">
-        <v>7211635</v>
+        <v>7211643</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4984,32 +4970,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127288433</v>
+        <v>127288438</v>
       </c>
       <c r="B43" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5019,10 +5005,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>753330</v>
+        <v>753284</v>
       </c>
       <c r="R43" t="n">
-        <v>7211606</v>
+        <v>7211602</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5085,53 +5071,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127288419</v>
+        <v>127288439</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>753103</v>
+        <v>753269</v>
       </c>
       <c r="R44" t="n">
-        <v>7211845</v>
+        <v>7211606</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5164,11 +5142,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5199,32 +5172,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127288455</v>
+        <v>127288440</v>
       </c>
       <c r="B45" t="n">
-        <v>80184</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5234,10 +5207,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>753192</v>
+        <v>753266</v>
       </c>
       <c r="R45" t="n">
-        <v>7211856</v>
+        <v>7211612</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5300,53 +5273,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127288417</v>
+        <v>127288441</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>753086</v>
+        <v>753235</v>
       </c>
       <c r="R46" t="n">
-        <v>7211788</v>
+        <v>7211650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5379,11 +5344,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5414,10 +5374,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128533114</v>
+        <v>127288442</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5442,21 +5402,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kankberg, Vb</t>
+          <t>Röjmyrbrännet, Vb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>753134</v>
+        <v>753219</v>
       </c>
       <c r="R47" t="n">
-        <v>7211650</v>
+        <v>7211658</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5483,17 +5439,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5508,15 +5459,443 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128533114</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kankberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>753134</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7211650</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
+      <c r="AX48" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127288424</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>753214</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7211833</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127288425</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>753269</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7211606</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>111966178</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Röjmyrbrännet, Kankberg, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>753214</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7211703</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Jörn</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56645-2024 artfynd.xlsx
+++ b/artfynd/A 56645-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288458</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966181</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966177</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288454</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966180</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1402,6 +1437,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106229116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1503,6 +1543,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966179</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1604,6 +1649,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288444</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1705,6 +1755,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288445</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288447</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1917,6 +1977,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288448</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2018,6 +2083,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288449</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288450</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288451</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288452</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2422,6 +2507,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288453</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2527,6 +2617,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106229099</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2628,6 +2723,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966183</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2729,6 +2829,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288428</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2830,6 +2935,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288430</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2931,6 +3041,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288431</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3032,6 +3147,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288432</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3133,6 +3253,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288433</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3234,6 +3359,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288434</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3335,6 +3465,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288436</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3436,6 +3571,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288423</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3537,6 +3677,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966182</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3638,6 +3783,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288455</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3739,6 +3889,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288456</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3840,6 +3995,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288457</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3954,6 +4114,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288414</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4068,6 +4233,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288415</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4182,6 +4352,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288416</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4296,6 +4471,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288417</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4410,6 +4590,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288418</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4524,6 +4709,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288419</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4638,6 +4828,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288421</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4752,6 +4947,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288422</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4866,6 +5066,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288411</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4967,6 +5172,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288412</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5068,6 +5278,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288438</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5169,6 +5384,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288439</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5270,6 +5490,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288440</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5371,6 +5596,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288441</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5472,6 +5702,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288442</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5578,6 +5813,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128533114</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5679,6 +5919,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288424</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5780,6 +6025,11 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127288425</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5896,8 +6146,65 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111966178</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>